--- a/artfynd/A 14463-2023 artfynd.xlsx
+++ b/artfynd/A 14463-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14463-2023 artfynd.xlsx
+++ b/artfynd/A 14463-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110424647</v>
+        <v>112090134</v>
       </c>
       <c r="B2" t="n">
-        <v>44331</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102019</v>
+        <v>6443</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klubbsprötad bastardsvärmare</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zygaena minos</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Utmed riksväg 37/47 mellan Brusemåla - Färgshult, Sm</t>
+          <t>Utmed riksväg 37/47 Bockara-Århult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571442.0698333294</v>
+        <v>571251</v>
       </c>
       <c r="R2" t="n">
-        <v>6347839.312473879</v>
+        <v>6347784</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,50 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112090134</v>
+        <v>110424647</v>
       </c>
       <c r="B3" t="n">
-        <v>77041</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45045</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6443</v>
+        <v>102019</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Klubbsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Zygaena minos</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Utmed riksväg 37/47 Bockara-Århult, Sm</t>
+          <t>Utmed riksväg 37/47 mellan Brusemåla - Färgshult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571252</v>
+        <v>571442</v>
       </c>
       <c r="R3" t="n">
-        <v>6347784</v>
+        <v>6347839</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,50 +873,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112090132</v>
+        <v>110567917</v>
       </c>
       <c r="B4" t="n">
-        <v>99024</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45045</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>102019</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klubbsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Zygaena minos</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Utmed riksväg 37/47 Bockara-Århult, Sm</t>
+          <t>Rv 37/47 nära Ekelund, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571158</v>
+        <v>571217</v>
       </c>
       <c r="R4" t="n">
-        <v>6347747</v>
+        <v>6347810</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -963,12 +947,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,6 +986,335 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>110567919</v>
+      </c>
+      <c r="B5" t="n">
+        <v>45045</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102019</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Klubbsprötad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Zygaena minos</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nära Rv 37/47 vid Lammhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>571440</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6347854</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110567920</v>
+      </c>
+      <c r="B6" t="n">
+        <v>45045</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102019</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Klubbsprötad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Zygaena minos</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nära Rv 37/47 vid Lammhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>571513</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6347865</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>112090132</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Utmed riksväg 37/47 Bockara-Århult, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>571158</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6347747</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14463-2023 artfynd.xlsx
+++ b/artfynd/A 14463-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112090134</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110424647</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110567917</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110567919</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110567920</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1315,8 +1345,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112090132</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>